--- a/tests/fixtures/test_cases/t101_perfect_en.xlsx
+++ b/tests/fixtures/test_cases/t101_perfect_en.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="tbl1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="tbl2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="tbl3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,111 +425,61 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Employment (thousands)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Change (thousands)</t>
+          <t>Employment</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Goods-producing</t>
+          <t>Goods</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>4500.2</v>
       </c>
-      <c r="C2" t="n">
-        <v>45.1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Services-producing</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>15500.6</v>
       </c>
-      <c r="C3" t="n">
-        <v>120.4</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>320.5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-5.2</v>
+        <v>20000.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1580.4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>25.6</v>
+          <t>Source: Statistics Canada</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Total, all industries</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>20000.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>165.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Source: Statistics Canada, LFS, July 2026.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>..</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>..</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>E use with caution</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>E</t>
+          <t>Note: Seasonally adjusted.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -545,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,224 +505,49 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Unemployment rate (percent)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Participation rate (percent)</t>
+          <t>Rate</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ontario</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>65.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ontario</t>
+          <t>Quebec</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>65.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Quebec</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="C4" t="n">
-        <v>65.09999999999999</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>British Columbia</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>66.09999999999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Alberta</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>68.90000000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Manitoba</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>66.40000000000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Source: Statistics Canada, LFS, July 2026.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>..</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>..</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>E use with caution</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Province/Territory</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Population (thousands)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Quarterly change (percent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ontario</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>15996.7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Quebec</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>9024.9</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>British Columbia</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>5640.8</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Alberta</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4850.2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Source: Statistics Canada, Demography Division, Q2 2026.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>E</t>
+          <t>Source: StatCan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/test_cases/t101_perfect_en.xlsx
+++ b/tests/fixtures/test_cases/t101_perfect_en.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="tbl1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="tbl2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="tbl3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -425,61 +430,171 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>Employment (thousands)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change (thousands)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Change (percent)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Goods</t>
+          <t>Goods-producing sector</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>4500.2</v>
       </c>
+      <c r="C2" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15500.6</v>
+        <v>320.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20000.8</v>
+        <v>1580.4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Source: Statistics Canada</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Services-producing sector</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>15500.6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Note: Seasonally adjusted.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Trade</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3100.2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total, all industries</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>20000.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>confidential</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>..</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>..</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Source: Statistics Canada, Labour Force Survey, July 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>.. not available</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>..</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>..</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>..</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Note: x = confidential; .. = not available. Seasonally adjusted data.</t>
         </is>
       </c>
     </row>
@@ -494,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,49 +620,209 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Rate</t>
+          <t>Unemployment rate (percent)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Participation rate (percent)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ontario</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>65.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Quebec</t>
+          <t>Ontario</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>65.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>Quebec</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Source: StatCan</t>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>66.09999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>68.90000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Source: Statistics Canada, LFS, July 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>.. not available for all territories.</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>..</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>..</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Note: x = confidential; .. = not available.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Province/Territory</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Population (thousands)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Quarterly change (percent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>15996.7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Quebec</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9024.9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5640.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>confidential</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>..</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Source: Statistics Canada, Demography Division, Q2 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Note: x = confidential; .. = not available. Preliminary estimates.</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/test_cases/t101_perfect_en.xlsx
+++ b/tests/fixtures/test_cases/t101_perfect_en.xlsx
@@ -575,21 +575,6 @@
           <t>.. not available</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>..</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>..</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>..</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -707,16 +692,6 @@
           <t>.. not available for all territories.</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>..</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>..</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
